--- a/ChatAFL-master/key_experiment/vulnerability/lightftp_漏洞发现_20260607222551.xlsx
+++ b/ChatAFL-master/key_experiment/vulnerability/lightftp_漏洞发现_20260607222551.xlsx
@@ -77,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -86,6 +86,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -451,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J292"/>
+  <dimension ref="A1:K292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -464,6 +467,7 @@
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -515,6 +519,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>为什么算漏洞</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>漏洞带来的影响</t>
         </is>
       </c>
     </row>
@@ -588,6 +597,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -685,6 +701,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -767,6 +793,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -838,6 +875,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -921,6 +966,14 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -1016,6 +1069,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1089,6 +1152,14 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1161,6 +1232,14 @@
 AFLNet协议Oracle检测到: FTP: PASS accepted without USER (auth state bypass) (类别0x0005, 严重等级4)</t>
         </is>
       </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1229,6 +1308,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -1312,6 +1399,17 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -1407,6 +1505,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1487,6 +1598,17 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -1586,6 +1708,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1676,6 +1808,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1770,6 +1912,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1844,6 +1997,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -1929,6 +2090,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2002,6 +2173,14 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2074,6 +2253,14 @@
 AFLNet协议Oracle检测到: FTP: Path traversal command accepted by server (类别0x0010, 严重等级4)</t>
         </is>
       </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2145,6 +2332,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -2224,6 +2418,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2299,6 +2504,16 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)
 AFLNet协议Oracle检测到: FTP: Multiple format string specifiers in command (format string vuln risk) (类别0x0020, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -2415,6 +2630,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2498,6 +2726,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2573,6 +2812,17 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -2688,6 +2938,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2759,6 +3022,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -2844,6 +3115,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2919,6 +3200,14 @@
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)</t>
         </is>
       </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2989,6 +3278,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -3084,6 +3380,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3155,6 +3461,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -3253,6 +3567,19 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -3368,6 +3695,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3450,6 +3790,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3524,6 +3874,13 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3591,6 +3948,14 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3660,6 +4025,14 @@
 AFLNet协议Oracle检测到: FTP: Path traversal command accepted by server (类别0x0010, 严重等级4)</t>
         </is>
       </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3725,6 +4098,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -3805,6 +4186,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3878,6 +4269,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -3974,6 +4373,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4057,6 +4469,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4138,6 +4560,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4209,6 +4642,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -4296,6 +4737,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4366,6 +4817,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -4442,6 +4900,14 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4507,6 +4973,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -4604,6 +5077,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4682,6 +5168,16 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -4819,6 +5315,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4954,6 +5463,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -5024,6 +5546,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -5119,6 +5648,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -5187,6 +5726,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -5276,6 +5822,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -5344,6 +5900,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -5418,6 +5982,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -5509,6 +6080,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -5590,6 +6171,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -5657,6 +6249,14 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -5728,6 +6328,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -5811,6 +6419,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -5891,6 +6510,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -5966,6 +6595,14 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -6037,6 +6674,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -6119,6 +6764,17 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -6208,6 +6864,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -6290,6 +6959,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -6371,6 +7051,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -6455,6 +7145,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -6539,6 +7239,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -6620,6 +7330,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -6692,6 +7413,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -6778,6 +7507,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -6843,6 +7582,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -6947,6 +7694,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -7018,6 +7778,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -7101,6 +7868,17 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -7206,6 +7984,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -7289,6 +8080,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -7370,6 +8172,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -7445,6 +8257,17 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -7539,6 +8362,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -7631,6 +8464,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -7703,6 +8549,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -7809,6 +8663,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -7884,6 +8751,14 @@
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)</t>
         </is>
       </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -7953,6 +8828,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -8040,6 +8922,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -8111,6 +9003,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -8238,6 +9138,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -8343,6 +9256,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -8428,6 +9354,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -8510,6 +9446,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -8577,6 +9523,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -8657,6 +9610,16 @@
 AFLNet协议Oracle检测到: FTP: Multiple format string specifiers in command (format string vuln risk) (类别0x0020, 严重等级3)</t>
         </is>
       </c>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -8729,6 +9692,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -8815,6 +9786,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -8899,6 +9880,14 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -8983,6 +9972,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -9067,6 +10066,16 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -9163,6 +10172,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -9245,6 +10265,14 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -9341,6 +10369,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -9410,6 +10448,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -9487,6 +10532,14 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -9599,6 +10652,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -9692,6 +10758,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -9783,6 +10859,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -9888,6 +10974,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -9960,6 +11059,13 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -10027,6 +11133,13 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -10098,6 +11211,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -10178,6 +11299,16 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)
 AFLNet协议Oracle检测到: FTP: Multiple format string specifiers in command (format string vuln risk) (类别0x0020, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -10273,6 +11404,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -10341,6 +11482,13 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -10411,6 +11559,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -10493,6 +11649,17 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PASS accepted without USER (auth state bypass) (类别0x0005, 严重等级4)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -10607,6 +11774,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -10680,6 +11857,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -10760,6 +11945,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -10832,6 +12027,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -10918,6 +12121,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K126" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -10990,6 +12203,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -11065,6 +12285,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K128" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -11190,6 +12418,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K129" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -11282,6 +12523,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -11364,6 +12615,16 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K131" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -11486,6 +12747,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -11624,6 +12898,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -11701,6 +12988,16 @@
 AFLNet协议Oracle检测到: FTP: Multiple format string specifiers in command (format string vuln risk) (类别0x0020, 严重等级3)</t>
         </is>
       </c>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -11786,6 +13083,13 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -11860,6 +13164,13 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -11930,6 +13241,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -12006,6 +13325,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K138" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -12094,6 +13420,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -12177,6 +13513,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -12248,6 +13595,14 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -12313,6 +13668,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -12419,6 +13782,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -12505,6 +13878,14 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -12578,6 +13959,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -12667,6 +14056,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -12749,6 +14151,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -12830,6 +14242,16 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PASS accepted without USER (auth state bypass) (类别0x0005, 严重等级4)
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -12931,6 +14353,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -12996,6 +14431,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -13085,6 +14528,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K151" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -13154,6 +14607,13 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -13225,6 +14685,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K153" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -13314,6 +14782,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K154" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -13384,6 +14865,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -13466,6 +14954,17 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K156" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -13553,6 +15052,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)
 AFLNet协议Oracle检测到: FTP: Multiple format string specifiers in command (format string vuln risk) (类别0x0020, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -13660,6 +15169,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K158" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -13737,6 +15259,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K159" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -13821,6 +15354,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -13901,6 +15444,17 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K161" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -13997,6 +15551,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K162" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -14091,6 +15655,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -14180,6 +15757,19 @@
 AFLNet协议Oracle检测到: FTP: Path traversal command accepted by server (类别0x0010, 严重等级4)
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K164" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -14319,6 +15909,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K165" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -14410,6 +16013,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K166" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -14482,6 +16095,14 @@
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)</t>
         </is>
       </c>
+      <c r="K167" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -14552,6 +16173,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K168" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -14634,6 +16262,13 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K169" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -14731,6 +16366,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K170" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -14796,6 +16441,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: Multiple format string specifiers in command (format string vuln risk) (类别0x0020, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K171" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -14872,6 +16524,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K172" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -14967,6 +16627,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K173" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -15046,6 +16719,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K174" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -15129,6 +16812,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K175" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -15213,6 +16906,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K176" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -15283,6 +16986,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K177" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -15363,6 +17073,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K178" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -15433,6 +17153,14 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K179" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -15498,6 +17226,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K180" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -15585,6 +17321,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K181" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -15666,6 +17412,14 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K182" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -15762,6 +17516,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K183" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -15851,6 +17615,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K184" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -15934,6 +17711,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K185" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -16001,6 +17788,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: Multiple format string specifiers in command (format string vuln risk) (类别0x0020, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K186" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -16076,6 +17870,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K187" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -16165,6 +17967,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K188" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -16241,6 +18053,13 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K189" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -16308,6 +18127,14 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K190" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -16374,6 +18201,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: Path traversal command accepted by server (类别0x0010, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K191" s="4" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -16456,6 +18291,13 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K192" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -16539,6 +18381,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K193" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -16612,6 +18464,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K194" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -16708,6 +18568,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K195" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -16784,6 +18657,16 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: Path traversal command accepted by server (类别0x0010, 严重等级4)
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K196" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -16873,6 +18756,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K197" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -16948,6 +18844,13 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K198" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -17019,6 +18922,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K199" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -17106,6 +19016,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K200" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -17179,6 +19099,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K201" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -17265,6 +19193,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K202" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -17337,6 +19275,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K203" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -17416,6 +19361,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K204" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -17498,6 +19453,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K205" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -17568,6 +19534,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K206" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -17642,6 +19616,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K207" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -17726,6 +19708,17 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PASS accepted without USER (auth state bypass) (类别0x0005, 严重等级4)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K208" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -17820,6 +19813,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K209" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -17904,6 +19907,14 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K210" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -17979,6 +19990,17 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K211" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -18084,6 +20106,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K212" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -18163,6 +20198,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K213" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -18245,6 +20291,16 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K214" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -18350,6 +20406,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K215" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -18443,6 +20509,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K216" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -18512,6 +20591,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K217" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -18595,6 +20682,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K218" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -18667,6 +20764,14 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K219" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -18735,6 +20840,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: Path traversal command accepted by server (类别0x0010, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K220" s="4" t="inlineStr">
+        <is>
+          <t>【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -18819,6 +20932,13 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K221" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -18896,6 +21016,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K222" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -18971,6 +21102,16 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)
 AFLNet协议Oracle检测到: FTP: Multiple format string specifiers in command (format string vuln risk) (类别0x0020, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K223" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -19067,6 +21208,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K224" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -19161,6 +21315,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K225" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -19255,6 +21420,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K226" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -19347,6 +21522,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K227" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -19419,6 +21607,14 @@
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)</t>
         </is>
       </c>
+      <c r="K228" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -19492,6 +21688,14 @@
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)</t>
         </is>
       </c>
+      <c r="K229" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -19564,6 +21768,14 @@
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)</t>
         </is>
       </c>
+      <c r="K230" s="4" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -19634,6 +21846,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K231" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -19760,6 +21979,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K232" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -19841,6 +22070,14 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K233" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -19967,6 +22204,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K234" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -20057,6 +22307,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K235" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -20141,6 +22404,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K236" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -20213,6 +22486,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K237" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -20359,6 +22639,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K238" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -20426,6 +22719,14 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K239" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -20492,6 +22793,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K240" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -20606,6 +22915,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K241" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -20671,6 +22990,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K242" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -20795,6 +23122,16 @@
 AFLNet协议Oracle检测到: FTP: Excessive failed authentication attempts (resource exhaustion risk) (类别0x00c0, 严重等级2)</t>
         </is>
       </c>
+      <c r="K243" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -20886,6 +23223,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K244" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -20952,6 +23299,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K245" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -21035,6 +23389,14 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K246" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -21141,6 +23503,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K247" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -21214,6 +23586,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K248" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -21295,6 +23674,14 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K249" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -21420,6 +23807,16 @@
 AFLNet协议Oracle检测到: FTP: Excessive failed authentication attempts (resource exhaustion risk) (类别0x00c0, 严重等级2)</t>
         </is>
       </c>
+      <c r="K250" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -21492,6 +23889,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K251" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -21577,6 +23981,17 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: RNTO without prior RNFR accepted by server (类别0x0004, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K252" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -21687,6 +24102,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K253" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -21791,6 +24219,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K254" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -21873,6 +24311,16 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K255" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -22009,6 +24457,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K256" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -22121,6 +24582,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K257" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -22189,6 +24663,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K258" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -22294,6 +24775,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K259" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -22366,6 +24860,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K260" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -22462,6 +24964,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K261" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -22527,6 +25039,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K262" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -22662,6 +25182,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K263" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -22739,6 +25272,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K264" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -22809,6 +25353,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K265" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -22895,6 +25446,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K266" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -22980,6 +25541,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K267" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -23062,6 +25634,16 @@
 AFLNet协议Oracle检测到: FTP: Multiple format string specifiers in command (format string vuln risk) (类别0x0020, 严重等级3)</t>
         </is>
       </c>
+      <c r="K268" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -23132,6 +25714,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K269" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -23206,6 +25796,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K270" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -23292,6 +25890,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K271" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -23377,6 +25986,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K272" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -23456,6 +26075,14 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K273" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -23549,6 +26176,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K274" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【敏感文件读取】攻击者可利用LightFTP的路径遍历漏洞读取服务器文件系统中的任意文件，包括/etc/passwd、/etc/shadow、SSH私钥、SSL证书私钥、应用配置文件（含数据库密码、API密钥）、日志文件（含会话令牌、用户IP）等高度敏感信息。
+【源代码泄露】若LightFTP为Web/应用服务器，攻击者可读取应用源代码，从中发现更多安全漏洞（硬编码凭据、SQL注入点、反序列化入口等），形成漏洞利用链。
+【远程代码执行前置】路径遍历通常作为攻击链的第一阶段——攻击者读取配置文件获取凭据后，进一步通过SSH/数据库连接获取Shell，或利用读取到的密钥材料伪造签名/解密敏感通信。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -23631,6 +26271,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K275" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【认证/授权绕过】LightFTP的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LightFTP进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -23715,6 +26366,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K276" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -23793,6 +26454,17 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K277" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -23865,6 +26537,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K278" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -23948,6 +26628,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K279" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -24021,6 +26711,13 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
         </is>
       </c>
+      <c r="K280" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -24086,6 +26783,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K281" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -24182,6 +26887,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K282" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -24254,6 +26972,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K283" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -24331,6 +27056,16 @@
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)
 AFLNet协议Oracle检测到: FTP: Multiple format string specifiers in command (format string vuln risk) (类别0x0020, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K284" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -24424,6 +27159,16 @@
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K285" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -24569,6 +27314,19 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K286" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -24649,6 +27407,16 @@
 AFLNet协议Oracle检测到: FTP: Multiple format string specifiers in command (format string vuln risk) (类别0x0020, 严重等级3)</t>
         </is>
       </c>
+      <c r="K287" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -24718,6 +27486,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K288" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -24792,6 +27567,13 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)</t>
+        </is>
+      </c>
+      <c r="K289" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -24873,6 +27655,16 @@
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
         </is>
       </c>
+      <c r="K290" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -24941,6 +27733,14 @@
         <is>
           <t>AFLNet协议Oracle在fuzzing过程中检测到FTP协议安全不变性被破坏:
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K291" s="4" t="inlineStr">
+        <is>
+          <t>【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -25028,6 +27828,19 @@
 AFLNet协议Oracle检测到: FTP: PASS accepted without USER (auth state bypass) (类别0x0005, 严重等级4)
 AFLNet协议Oracle检测到: FTP: CRLF injection in command arguments (FTP command smuggling) (类别0x0020, 严重等级4)
 AFLNet协议Oracle检测到: FTP: PORT command specifies private/internal address (FTP bounce risk) (类别0x0100, 严重等级3)</t>
+        </is>
+      </c>
+      <c r="K292" s="4" t="inlineStr">
+        <is>
+          <t>【FTP命令走私】攻击者可利用LightFTP的CRLF注入漏洞在FTP协议参数中嵌入额外的FTP命令。当LightFTP未正确处理输入中的CR/LF字符时，攻击者可注入任意FTP命令，包括文件上传/下载、目录遍历、权限修改等操作，实质上绕过所有FTP级别的访问控制。
+【横向移动与内网渗透】通过FTP命令走私，攻击者可利用已攻陷的FTP客户端或中间节点作为跳板，向内部网络中的其他主机发起FTP命令，实现内网横向移动。
+【内网端口扫描与拓扑探测】攻击者可利用LightFTP作为代理，通过FTP PORT命令将数据连接重定向到内部网络任意IP:端口。通过分析连接成功/失败的响应差异，攻击者可以扫描LightFTP所在内网的端口开放情况和网络拓扑结构，为后续定向攻击提供情报支撑。
+【防火墙/NAT绕过】FTP Bounce攻击使攻击者能够绕过防火墙对内部网络的访问限制，通过LightFTP这个合法FTP服务作为跳板访问本不应可达的内部资源。
+【匿名攻击溯源困难】攻击者通过LightFTP发起对内网其他主机的攻击，日志仅记录LightFTP的连接而难以追踪真实攻击源IP。
+【未授权访问】攻击者可绕过LightFTP的身份认证机制，无需提供有效凭据即可访问受保护的服务功能和数据。这相当于将LightFTP的认证门控完全失效，任何能够网络连接到服务的攻击者均可获得已认证用户的权限。
+【数据泄露与篡改】认证绕过后，攻击者可读取、修改、删除LightFTP管理的所有数据，包括敏感配置文件、用户数据、媒体内容等。若LightFTP连接到其他后端系统，攻击面将进一步扩大。
+【权限提升跳板】认证绕过通常可作为进一步攻击的跳板——攻击者获取立足点后可利用其他漏洞（如路径遍历、命令注入）扩大控制范围。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
